--- a/docs/요구사항_정의서.xlsx
+++ b/docs/요구사항_정의서.xlsx
@@ -5080,263 +5080,903 @@
       <c r="K91" s="42" t="n"/>
     </row>
     <row r="92" ht="22.5" customHeight="1" s="92">
-      <c r="A92" s="60" t="n"/>
-      <c r="B92" s="61" t="n"/>
-      <c r="C92" s="61" t="n"/>
-      <c r="D92" s="61" t="n"/>
-      <c r="E92" s="61" t="n"/>
-      <c r="F92" s="62" t="n"/>
-      <c r="G92" s="63" t="n"/>
-      <c r="H92" s="64" t="n"/>
-      <c r="I92" s="62" t="n"/>
-      <c r="J92" s="65" t="n"/>
-      <c r="K92" s="37" t="n"/>
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>REQ-063</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="n"/>
+      <c r="E92" s="32" t="n"/>
+      <c r="F92" s="33" t="inlineStr">
+        <is>
+          <t>일반 사용자는 로그아웃할 수 있어야 하며, 로그아웃 시 서버는 access/refresh token의 JTI를 블랙리스트에 등록하고 refresh token 쿠키를 삭제해야 한다.</t>
+        </is>
+      </c>
+      <c r="G92" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H92" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I92" s="59" t="inlineStr">
+        <is>
+          <t>JTI 블랙리스트 기반</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K92" s="42" t="n"/>
     </row>
     <row r="93" ht="22.5" customHeight="1" s="92">
-      <c r="A93" s="66" t="n"/>
-      <c r="B93" s="67" t="n"/>
-      <c r="C93" s="67" t="n"/>
-      <c r="D93" s="67" t="n"/>
-      <c r="E93" s="67" t="n"/>
-      <c r="F93" s="68" t="n"/>
-      <c r="G93" s="69" t="n"/>
-      <c r="H93" s="70" t="n"/>
-      <c r="I93" s="68" t="n"/>
-      <c r="J93" s="71" t="n"/>
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>REQ-064</t>
+        </is>
+      </c>
+      <c r="B93" s="32" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>내 정보 조회</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="n"/>
+      <c r="E93" s="32" t="n"/>
+      <c r="F93" s="33" t="inlineStr">
+        <is>
+          <t>일반 사용자는 본인의 이름, 이메일, 전화번호, 생년월일, 성별, 가입일 등 개인 정보를 조회할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G93" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H93" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I93" s="59" t="inlineStr">
+        <is>
+          <t>Bearer 토큰 기반 식별</t>
+        </is>
+      </c>
+      <c r="J93" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K93" s="42" t="n"/>
     </row>
     <row r="94" ht="22.5" customHeight="1" s="92">
-      <c r="A94" s="60" t="n"/>
-      <c r="B94" s="61" t="n"/>
-      <c r="C94" s="61" t="n"/>
-      <c r="D94" s="72" t="n"/>
-      <c r="E94" s="72" t="n"/>
-      <c r="F94" s="62" t="n"/>
-      <c r="G94" s="63" t="n"/>
-      <c r="H94" s="73" t="n"/>
-      <c r="I94" s="72" t="n"/>
-      <c r="J94" s="65" t="n"/>
-      <c r="K94" s="37" t="n"/>
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>REQ-065</t>
+        </is>
+      </c>
+      <c r="B94" s="32" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>내 정보 수정</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="n"/>
+      <c r="E94" s="32" t="n"/>
+      <c r="F94" s="33" t="inlineStr">
+        <is>
+          <t>일반 사용자는 본인의 이름, 이메일, 전화번호, 생년월일, 성별을 부분 수정(PATCH)할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G94" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H94" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I94" s="59" t="inlineStr">
+        <is>
+          <t>이메일/전화번호 중복 검증 포함</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K94" s="42" t="n"/>
     </row>
     <row r="95" ht="22.5" customHeight="1" s="92">
-      <c r="A95" s="66" t="n"/>
-      <c r="B95" s="67" t="n"/>
-      <c r="C95" s="67" t="n"/>
-      <c r="D95" s="67" t="n"/>
-      <c r="E95" s="74" t="n"/>
-      <c r="F95" s="68" t="n"/>
-      <c r="G95" s="69" t="n"/>
-      <c r="H95" s="75" t="n"/>
-      <c r="I95" s="74" t="n"/>
-      <c r="J95" s="71" t="n"/>
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>REQ-066</t>
+        </is>
+      </c>
+      <c r="B95" s="32" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>알림 설정 관리</t>
+        </is>
+      </c>
+      <c r="D95" s="32" t="n"/>
+      <c r="E95" s="32" t="n"/>
+      <c r="F95" s="33" t="inlineStr">
+        <is>
+          <t>일반 사용자는 카테고리별 알림 수신 설정(홈 일정, 식사, 복약, 운동, 수면, 약 소진 D-day)을 조회 및 수정할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G95" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H95" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I95" s="59" t="inlineStr">
+        <is>
+          <t>선택 기능</t>
+        </is>
+      </c>
+      <c r="J95" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K95" s="42" t="n"/>
     </row>
     <row r="96" ht="22.5" customHeight="1" s="92">
-      <c r="A96" s="60" t="n"/>
-      <c r="B96" s="61" t="n"/>
-      <c r="C96" s="61" t="n"/>
-      <c r="D96" s="61" t="n"/>
-      <c r="E96" s="72" t="n"/>
-      <c r="F96" s="62" t="n"/>
-      <c r="G96" s="63" t="n"/>
-      <c r="H96" s="73" t="n"/>
-      <c r="I96" s="72" t="n"/>
-      <c r="J96" s="65" t="n"/>
-      <c r="K96" s="37" t="n"/>
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>REQ-067</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>읽은 알림 삭제</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="n"/>
+      <c r="E96" s="32" t="n"/>
+      <c r="F96" s="33" t="inlineStr">
+        <is>
+          <t>일반 사용자는 읽음 처리된 알림을 일괄 삭제할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G96" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H96" s="44" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I96" s="59" t="inlineStr">
+        <is>
+          <t>선택 기능</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K96" s="42" t="n"/>
     </row>
     <row r="97" ht="22.5" customHeight="1" s="92">
-      <c r="A97" s="66" t="n"/>
-      <c r="B97" s="67" t="n"/>
-      <c r="C97" s="67" t="n"/>
-      <c r="D97" s="74" t="n"/>
-      <c r="E97" s="74" t="n"/>
-      <c r="F97" s="68" t="n"/>
-      <c r="G97" s="69" t="n"/>
-      <c r="H97" s="75" t="n"/>
-      <c r="I97" s="74" t="n"/>
-      <c r="J97" s="74" t="n"/>
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>REQ-068</t>
+        </is>
+      </c>
+      <c r="B97" s="32" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C97" s="32" t="inlineStr">
+        <is>
+          <t>약물 상세 정보 조회</t>
+        </is>
+      </c>
+      <c r="D97" s="32" t="n"/>
+      <c r="E97" s="32" t="n"/>
+      <c r="F97" s="33" t="inlineStr">
+        <is>
+          <t>시스템은 약물명으로 효능, 용법, 주의사항, 부작용, 상호작용, 보관방법 등 상세 정보를 조회할 수 있어야 하며, DB → 외부 API(공공데이터) → LLM 순으로 3단계 폴백을 적용한다.</t>
+        </is>
+      </c>
+      <c r="G97" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H97" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I97" s="59" t="inlineStr">
+        <is>
+          <t>3-tier 폴백</t>
+        </is>
+      </c>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K97" s="42" t="n"/>
     </row>
     <row r="98" ht="22.5" customHeight="1" s="92">
-      <c r="A98" s="60" t="n"/>
-      <c r="B98" s="61" t="n"/>
-      <c r="C98" s="61" t="n"/>
-      <c r="D98" s="72" t="n"/>
-      <c r="E98" s="72" t="n"/>
-      <c r="F98" s="62" t="n"/>
-      <c r="G98" s="63" t="n"/>
-      <c r="H98" s="76" t="n"/>
-      <c r="I98" s="62" t="n"/>
-      <c r="J98" s="72" t="n"/>
-      <c r="K98" s="37" t="n"/>
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>REQ-069</t>
+        </is>
+      </c>
+      <c r="B98" s="32" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>ADHD 약물 DB 검색</t>
+        </is>
+      </c>
+      <c r="D98" s="32" t="n"/>
+      <c r="E98" s="32" t="n"/>
+      <c r="F98" s="33" t="inlineStr">
+        <is>
+          <t>시스템은 ADHD 관련 정신건강의학과 약물 데이터베이스에서 제품명 기반 검색을 제공하고, 성분명/부작용/주의사항 정보를 반환해야 한다.</t>
+        </is>
+      </c>
+      <c r="G98" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H98" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I98" s="59" t="inlineStr">
+        <is>
+          <t>PsychDrug 테이블</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K98" s="42" t="n"/>
     </row>
     <row r="99" ht="22.5" customHeight="1" s="92">
-      <c r="A99" s="66" t="n"/>
-      <c r="B99" s="67" t="n"/>
-      <c r="C99" s="67" t="n"/>
-      <c r="D99" s="74" t="n"/>
-      <c r="E99" s="74" t="n"/>
-      <c r="F99" s="68" t="n"/>
-      <c r="G99" s="69" t="n"/>
-      <c r="H99" s="77" t="n"/>
-      <c r="I99" s="68" t="n"/>
-      <c r="J99" s="74" t="n"/>
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>REQ-070</t>
+        </is>
+      </c>
+      <c r="B99" s="32" t="inlineStr">
+        <is>
+          <t>가이드</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>가이드 스냅샷 확정+생성</t>
+        </is>
+      </c>
+      <c r="D99" s="32" t="n"/>
+      <c r="E99" s="32" t="n"/>
+      <c r="F99" s="33" t="inlineStr">
+        <is>
+          <t>OCR 결과 확정과 가이드 생성 작업을 단일 요청으로 처리하여 프론트엔드의 2-step 호출을 1-step으로 최적화할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G99" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H99" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I99" s="59" t="inlineStr">
+        <is>
+          <t>confirm-and-create 통합 API</t>
+        </is>
+      </c>
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K99" s="42" t="n"/>
     </row>
     <row r="100" ht="22.5" customHeight="1" s="92">
-      <c r="A100" s="60" t="n"/>
-      <c r="B100" s="61" t="n"/>
-      <c r="C100" s="61" t="n"/>
-      <c r="D100" s="61" t="n"/>
-      <c r="E100" s="72" t="n"/>
-      <c r="F100" s="62" t="n"/>
-      <c r="G100" s="63" t="n"/>
-      <c r="H100" s="73" t="n"/>
-      <c r="I100" s="62" t="n"/>
-      <c r="J100" s="65" t="n"/>
-      <c r="K100" s="37" t="n"/>
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>REQ-071</t>
+        </is>
+      </c>
+      <c r="B100" s="32" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="inlineStr">
+        <is>
+          <t>복약 리마인더 자동 비활성화</t>
+        </is>
+      </c>
+      <c r="D100" s="32" t="n"/>
+      <c r="E100" s="32" t="n"/>
+      <c r="F100" s="33" t="inlineStr">
+        <is>
+          <t>약 소진 예상일이 경과한 리마인더는 시스템이 주기적(1시간 간격)으로 자동 비활성화(enabled=false)해야 한다.</t>
+        </is>
+      </c>
+      <c r="G100" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H100" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I100" s="59" t="inlineStr">
+        <is>
+          <t>백그라운드 태스크</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K100" s="42" t="n"/>
     </row>
     <row r="101" ht="22.5" customHeight="1" s="92">
-      <c r="A101" s="66" t="n"/>
-      <c r="B101" s="67" t="n"/>
-      <c r="C101" s="67" t="n"/>
-      <c r="D101" s="67" t="n"/>
-      <c r="E101" s="74" t="n"/>
-      <c r="F101" s="68" t="n"/>
-      <c r="G101" s="69" t="n"/>
-      <c r="H101" s="75" t="n"/>
-      <c r="I101" s="68" t="n"/>
-      <c r="J101" s="74" t="n"/>
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>REQ-072</t>
+        </is>
+      </c>
+      <c r="B101" s="32" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C101" s="32" t="inlineStr">
+        <is>
+          <t>알림 중복 방지</t>
+        </is>
+      </c>
+      <c r="D101" s="32" t="n"/>
+      <c r="E101" s="32" t="n"/>
+      <c r="F101" s="33" t="inlineStr">
+        <is>
+          <t>동일 사용자에게 같은 유형의 알림(건강 경고, D-day 등)이 같은 날 중복 생성되지 않도록 캐시 기반 중복 검사를 수행해야 한다.</t>
+        </is>
+      </c>
+      <c r="G101" s="34" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H101" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I101" s="59" t="inlineStr">
+        <is>
+          <t>TTL 캐시(5분)</t>
+        </is>
+      </c>
+      <c r="J101" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K101" s="42" t="n"/>
     </row>
     <row r="102" ht="22.5" customHeight="1" s="92">
-      <c r="A102" s="60" t="n"/>
-      <c r="B102" s="61" t="n"/>
-      <c r="C102" s="61" t="n"/>
-      <c r="D102" s="61" t="n"/>
-      <c r="E102" s="61" t="n"/>
-      <c r="F102" s="62" t="n"/>
-      <c r="G102" s="63" t="n"/>
-      <c r="H102" s="73" t="n"/>
-      <c r="I102" s="62" t="n"/>
-      <c r="J102" s="72" t="n"/>
-      <c r="K102" s="37" t="n"/>
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>REQ-129</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>JWT 토큰 로테이션</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="n"/>
+      <c r="E102" s="32" t="n"/>
+      <c r="F102" s="33" t="inlineStr">
+        <is>
+          <t>토큰 재발급 시 기존 refresh token을 즉시 폐기하고 새 refresh token을 발급(로테이션)하여, 탈취된 토큰의 재사용을 방지해야 한다.</t>
+        </is>
+      </c>
+      <c r="G102" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H102" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I102" s="59" t="inlineStr">
+        <is>
+          <t>Refresh Token Rotation</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K102" s="42" t="n"/>
     </row>
     <row r="103" ht="22.5" customHeight="1" s="92">
-      <c r="A103" s="66" t="n"/>
-      <c r="B103" s="67" t="n"/>
-      <c r="C103" s="67" t="n"/>
-      <c r="D103" s="74" t="n"/>
-      <c r="E103" s="74" t="n"/>
-      <c r="F103" s="68" t="n"/>
-      <c r="G103" s="69" t="n"/>
-      <c r="H103" s="75" t="n"/>
-      <c r="I103" s="68" t="n"/>
-      <c r="J103" s="74" t="n"/>
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>REQ-130</t>
+        </is>
+      </c>
+      <c r="B103" s="32" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C103" s="32" t="inlineStr">
+        <is>
+          <t>JTI 블랙리스트 토큰 폐기</t>
+        </is>
+      </c>
+      <c r="D103" s="32" t="n"/>
+      <c r="E103" s="32" t="n"/>
+      <c r="F103" s="33" t="inlineStr">
+        <is>
+          <t>모든 JWT에 고유 JTI(JWT ID) 클레임을 포함하고, 로그아웃/탈퇴 시 JTI를 Redis 블랙리스트에 등록하여 즉시 무효화해야 한다. Redis 장애 시 안전 우선(fail-closed) 정책을 적용한다.</t>
+        </is>
+      </c>
+      <c r="G103" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H103" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I103" s="59" t="inlineStr">
+        <is>
+          <t>Redis TTL 기반, fail-closed</t>
+        </is>
+      </c>
+      <c r="J103" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K103" s="42" t="n"/>
     </row>
     <row r="104" ht="22.5" customHeight="1" s="92">
-      <c r="A104" s="60" t="n"/>
-      <c r="B104" s="61" t="n"/>
-      <c r="C104" s="61" t="n"/>
-      <c r="D104" s="61" t="n"/>
-      <c r="E104" s="72" t="n"/>
-      <c r="F104" s="62" t="n"/>
-      <c r="G104" s="63" t="n"/>
-      <c r="H104" s="73" t="n"/>
-      <c r="I104" s="62" t="n"/>
-      <c r="J104" s="72" t="n"/>
-      <c r="K104" s="37" t="n"/>
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>REQ-131</t>
+        </is>
+      </c>
+      <c r="B104" s="32" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>CORS 정책</t>
+        </is>
+      </c>
+      <c r="D104" s="32" t="n"/>
+      <c r="E104" s="32" t="n"/>
+      <c r="F104" s="33" t="inlineStr">
+        <is>
+          <t>운영환경에서 FRONTEND_ORIGIN 환경변수에 명시된 도메인만 cross-origin 요청을 허용하고, 미설정 시 모든 cross-origin 요청을 차단해야 한다.</t>
+        </is>
+      </c>
+      <c r="G104" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H104" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I104" s="59" t="inlineStr">
+        <is>
+          <t>credentials 포함</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K104" s="42" t="n"/>
     </row>
     <row r="105" ht="22.5" customHeight="1" s="92">
-      <c r="A105" s="66" t="n"/>
-      <c r="B105" s="67" t="n"/>
-      <c r="C105" s="67" t="n"/>
-      <c r="D105" s="67" t="n"/>
-      <c r="E105" s="74" t="n"/>
-      <c r="F105" s="68" t="n"/>
-      <c r="G105" s="69" t="n"/>
-      <c r="H105" s="77" t="n"/>
-      <c r="I105" s="74" t="n"/>
-      <c r="J105" s="74" t="n"/>
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>REQ-132</t>
+        </is>
+      </c>
+      <c r="B105" s="32" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>비밀번호 강도 검증</t>
+        </is>
+      </c>
+      <c r="D105" s="32" t="n"/>
+      <c r="E105" s="32" t="n"/>
+      <c r="F105" s="33" t="inlineStr">
+        <is>
+          <t>회원가입 시 비밀번호는 최소 8자, 대문자/소문자/숫자/특수문자 각 1자 이상을 포함해야 하며, 미충족 시 가입을 거부해야 한다.</t>
+        </is>
+      </c>
+      <c r="G105" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H105" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I105" s="59" t="inlineStr">
+        <is>
+          <t>정규식 검증</t>
+        </is>
+      </c>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K105" s="42" t="n"/>
     </row>
     <row r="106" ht="22.5" customHeight="1" s="92">
-      <c r="A106" s="60" t="n"/>
-      <c r="B106" s="61" t="n"/>
-      <c r="C106" s="61" t="n"/>
-      <c r="D106" s="72" t="n"/>
-      <c r="E106" s="72" t="n"/>
-      <c r="F106" s="62" t="n"/>
-      <c r="G106" s="63" t="n"/>
-      <c r="H106" s="73" t="n"/>
-      <c r="I106" s="62" t="n"/>
-      <c r="J106" s="72" t="n"/>
-      <c r="K106" s="37" t="n"/>
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>REQ-133</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="inlineStr">
+        <is>
+          <t>성능</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>Nginx 요청 속도 제한</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="n"/>
+      <c r="E106" s="32" t="n"/>
+      <c r="F106" s="33" t="inlineStr">
+        <is>
+          <t>Nginx 리버스 프록시에서 인증 API(5req/s), OCR API(3req/s), 일반 API(30req/s) 별로 요청 속도를 제한하고, 초과 시 429를 반환해야 한다.</t>
+        </is>
+      </c>
+      <c r="G106" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H106" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I106" s="59" t="inlineStr">
+        <is>
+          <t>burst 허용</t>
+        </is>
+      </c>
+      <c r="J106" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K106" s="42" t="n"/>
     </row>
     <row r="107" ht="22.5" customHeight="1" s="92">
-      <c r="A107" s="66" t="n"/>
-      <c r="B107" s="67" t="n"/>
-      <c r="C107" s="67" t="n"/>
-      <c r="D107" s="74" t="n"/>
-      <c r="E107" s="74" t="n"/>
-      <c r="F107" s="68" t="n"/>
-      <c r="G107" s="69" t="n"/>
-      <c r="H107" s="75" t="n"/>
-      <c r="I107" s="68" t="n"/>
-      <c r="J107" s="74" t="n"/>
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>REQ-134</t>
+        </is>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>Docker 컨테이너화</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="n"/>
+      <c r="E107" s="32" t="n"/>
+      <c r="F107" s="33" t="inlineStr">
+        <is>
+          <t>API 서버, AI 워커, MySQL, Redis, ChromaDB, Nginx를 Docker Compose로 구성하고, 서비스 간 네트워크를 frontend/backend로 분리해야 한다.</t>
+        </is>
+      </c>
+      <c r="G107" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H107" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I107" s="59" t="inlineStr">
+        <is>
+          <t>멀티 서비스 구성</t>
+        </is>
+      </c>
+      <c r="J107" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K107" s="42" t="n"/>
     </row>
     <row r="108" ht="22.5" customHeight="1" s="92">
-      <c r="A108" s="60" t="n"/>
-      <c r="B108" s="61" t="n"/>
-      <c r="C108" s="61" t="n"/>
-      <c r="D108" s="72" t="n"/>
-      <c r="E108" s="72" t="n"/>
-      <c r="F108" s="62" t="n"/>
-      <c r="G108" s="63" t="n"/>
-      <c r="H108" s="76" t="n"/>
-      <c r="I108" s="62" t="n"/>
-      <c r="J108" s="72" t="n"/>
-      <c r="K108" s="37" t="n"/>
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>REQ-135</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>프론트엔드 토큰 자동 갱신</t>
+        </is>
+      </c>
+      <c r="D108" s="32" t="n"/>
+      <c r="E108" s="32" t="n"/>
+      <c r="F108" s="33" t="inlineStr">
+        <is>
+          <t>프론트엔드는 API 호출 시 401 응답을 수신하면 자동으로 토큰 재발급을 시도하고, 원래 요청을 재실행해야 한다. 동시 다발 401 시 재발급 요청을 단일화(deduplication)한다.</t>
+        </is>
+      </c>
+      <c r="G108" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H108" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I108" s="59" t="inlineStr">
+        <is>
+          <t>무중단 사용자 경험</t>
+        </is>
+      </c>
+      <c r="J108" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K108" s="42" t="n"/>
     </row>
     <row r="109" ht="22.5" customHeight="1" s="92">
-      <c r="A109" s="66" t="n"/>
-      <c r="B109" s="67" t="n"/>
-      <c r="C109" s="67" t="n"/>
-      <c r="D109" s="74" t="n"/>
-      <c r="E109" s="74" t="n"/>
-      <c r="F109" s="68" t="n"/>
-      <c r="G109" s="69" t="n"/>
-      <c r="H109" s="77" t="n"/>
-      <c r="I109" s="68" t="n"/>
-      <c r="J109" s="74" t="n"/>
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>REQ-136</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>프라이버시</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>사용자 전환 데이터 격리</t>
+        </is>
+      </c>
+      <c r="D109" s="32" t="n"/>
+      <c r="E109" s="32" t="n"/>
+      <c r="F109" s="33" t="inlineStr">
+        <is>
+          <t>동일 기기에서 다른 사용자로 로그인 시 이전 사용자의 OCR/가이드/챗봇 세션 등 로컬 데이터를 자동 정리하여 데이터 유출을 방지해야 한다.</t>
+        </is>
+      </c>
+      <c r="G109" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H109" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I109" s="59" t="inlineStr">
+        <is>
+          <t>localStorage 클린업</t>
+        </is>
+      </c>
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K109" s="42" t="n"/>
     </row>
     <row r="110" ht="22.5" customHeight="1" s="92">
-      <c r="A110" s="60" t="n"/>
-      <c r="B110" s="61" t="n"/>
-      <c r="C110" s="61" t="n"/>
-      <c r="D110" s="72" t="n"/>
-      <c r="E110" s="72" t="n"/>
-      <c r="F110" s="62" t="n"/>
-      <c r="G110" s="63" t="n"/>
-      <c r="H110" s="76" t="n"/>
-      <c r="I110" s="62" t="n"/>
-      <c r="J110" s="72" t="n"/>
-      <c r="K110" s="37" t="n"/>
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>REQ-137</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>DB 마이그레이션 자동 적용</t>
+        </is>
+      </c>
+      <c r="D110" s="32" t="n"/>
+      <c r="E110" s="32" t="n"/>
+      <c r="F110" s="33" t="inlineStr">
+        <is>
+          <t>서버 기동 시 pending 상태의 데이터베이스 마이그레이션을 자동으로 감지하고 순차 적용해야 한다.</t>
+        </is>
+      </c>
+      <c r="G110" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H110" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I110" s="59" t="inlineStr">
+        <is>
+          <t>Aerich 호환</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K110" s="42" t="n"/>
     </row>
     <row r="111" ht="22.5" customHeight="1" s="92">
-      <c r="A111" s="66" t="n"/>
-      <c r="B111" s="67" t="n"/>
-      <c r="C111" s="67" t="n"/>
-      <c r="D111" s="74" t="n"/>
-      <c r="E111" s="74" t="n"/>
-      <c r="F111" s="68" t="n"/>
-      <c r="G111" s="69" t="n"/>
-      <c r="H111" s="75" t="n"/>
-      <c r="I111" s="68" t="n"/>
-      <c r="J111" s="74" t="n"/>
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>REQ-138</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>Nginx 보안 헤더</t>
+        </is>
+      </c>
+      <c r="D111" s="32" t="n"/>
+      <c r="E111" s="32" t="n"/>
+      <c r="F111" s="33" t="inlineStr">
+        <is>
+          <t>Nginx에서 X-Content-Type-Options(nosniff), X-Frame-Options(DENY), X-XSS-Protection(1; mode=block) 보안 헤더를 모든 응답에 포함해야 한다.</t>
+        </is>
+      </c>
+      <c r="G111" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H111" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I111" s="59" t="inlineStr">
+        <is>
+          <t>OWASP 권장</t>
+        </is>
+      </c>
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K111" s="42" t="n"/>
     </row>
     <row r="112" ht="22.5" customHeight="1" s="92">

--- a/docs/요구사항_정의서.xlsx
+++ b/docs/요구사항_정의서.xlsx
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="K76" s="10" t="n"/>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J77" s="14" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="K77" s="10" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="K78" s="10" t="n"/>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J79" s="14" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="K79" s="37" t="n"/>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="K82" s="10" t="n"/>
@@ -5980,29 +5980,93 @@
       <c r="K111" s="42" t="n"/>
     </row>
     <row r="112" ht="22.5" customHeight="1" s="92">
-      <c r="A112" s="60" t="n"/>
-      <c r="B112" s="61" t="n"/>
-      <c r="C112" s="61" t="n"/>
+      <c r="A112" s="60" t="inlineStr">
+        <is>
+          <t>REQ-075</t>
+        </is>
+      </c>
+      <c r="B112" s="61" t="inlineStr">
+        <is>
+          <t>가이드</t>
+        </is>
+      </c>
+      <c r="C112" s="61" t="inlineStr">
+        <is>
+          <t>가이드 피드백 수집</t>
+        </is>
+      </c>
       <c r="D112" s="61" t="n"/>
       <c r="E112" s="72" t="n"/>
-      <c r="F112" s="62" t="n"/>
-      <c r="G112" s="63" t="n"/>
-      <c r="H112" s="76" t="n"/>
-      <c r="I112" s="62" t="n"/>
-      <c r="J112" s="72" t="n"/>
+      <c r="F112" s="62" t="inlineStr">
+        <is>
+          <t>일반 사용자는 생성된 가이드에 대해 별점(1~5), 도움 여부, 코멘트를 제출할 수 있어야 하며, 가이드당 사용자 1회만 허용한다. 피드백에는 가이드 생성 시 사용된 프롬프트 버전이 자동 기록된다.</t>
+        </is>
+      </c>
+      <c r="G112" s="63" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H112" s="76" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I112" s="62" t="inlineStr">
+        <is>
+          <t>unique(guide_job_id, user_id), rating 1~5 검증, comment 최대 1000자</t>
+        </is>
+      </c>
+      <c r="J112" s="72" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K112" s="37" t="n"/>
     </row>
     <row r="113" ht="22.5" customHeight="1" s="92">
-      <c r="A113" s="66" t="n"/>
-      <c r="B113" s="67" t="n"/>
-      <c r="C113" s="67" t="n"/>
+      <c r="A113" s="66" t="inlineStr">
+        <is>
+          <t>REQ-076</t>
+        </is>
+      </c>
+      <c r="B113" s="67" t="inlineStr">
+        <is>
+          <t>가이드</t>
+        </is>
+      </c>
+      <c r="C113" s="67" t="inlineStr">
+        <is>
+          <t>가이드 피드백 통계 조회</t>
+        </is>
+      </c>
       <c r="D113" s="67" t="n"/>
       <c r="E113" s="74" t="n"/>
-      <c r="F113" s="68" t="n"/>
-      <c r="G113" s="69" t="n"/>
-      <c r="H113" s="75" t="n"/>
-      <c r="I113" s="68" t="n"/>
-      <c r="J113" s="74" t="n"/>
+      <c r="F113" s="68" t="inlineStr">
+        <is>
+          <t>시스템은 프롬프트 버전별 평균 평점, 도움됨 비율을 집계하여 반환할 수 있어야 하며, 이를 통해 저평점 프롬프트 버전 식별 및 개선 판단 근거를 제공한다.</t>
+        </is>
+      </c>
+      <c r="G113" s="69" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H113" s="75" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I113" s="68" t="inlineStr">
+        <is>
+          <t>prompt_version별 그룹 집계</t>
+        </is>
+      </c>
+      <c r="J113" s="74" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K113" s="42" t="n"/>
     </row>
     <row r="114" ht="22.5" customHeight="1" s="92">

--- a/docs/요구사항_정의서.xlsx
+++ b/docs/요구사항_정의서.xlsx
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="K72" s="10" t="n"/>

--- a/docs/요구사항_정의서.xlsx
+++ b/docs/요구사항_정의서.xlsx
@@ -968,7 +968,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1004"/>
+  <dimension ref="A1:Z1006"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="92" min="1" max="1"/>
@@ -5530,99 +5530,99 @@
       <c r="K101" s="42" t="n"/>
     </row>
     <row r="102" ht="22.5" customHeight="1" s="92">
-      <c r="A102" s="14" t="inlineStr">
-        <is>
-          <t>REQ-129</t>
-        </is>
-      </c>
-      <c r="B102" s="32" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="C102" s="32" t="inlineStr">
-        <is>
-          <t>JWT 토큰 로테이션</t>
-        </is>
-      </c>
-      <c r="D102" s="32" t="n"/>
-      <c r="E102" s="32" t="n"/>
-      <c r="F102" s="33" t="inlineStr">
-        <is>
-          <t>토큰 재발급 시 기존 refresh token을 즉시 폐기하고 새 refresh token을 발급(로테이션)하여, 탈취된 토큰의 재사용을 방지해야 한다.</t>
-        </is>
-      </c>
-      <c r="G102" s="34" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H102" s="44" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I102" s="59" t="inlineStr">
-        <is>
-          <t>Refresh Token Rotation</t>
-        </is>
-      </c>
-      <c r="J102" s="14" t="inlineStr">
+      <c r="A102" s="91" t="inlineStr">
+        <is>
+          <t>REQ-073</t>
+        </is>
+      </c>
+      <c r="B102" s="91" t="inlineStr">
+        <is>
+          <t>일기</t>
+        </is>
+      </c>
+      <c r="C102" s="91" t="inlineStr">
+        <is>
+          <t>일기 저장/조회</t>
+        </is>
+      </c>
+      <c r="D102" s="91" t="n"/>
+      <c r="E102" s="91" t="n"/>
+      <c r="F102" s="91" t="inlineStr">
+        <is>
+          <t>일반 사용자는 날짜별 일기를 저장하고 조회할 수 있어야 하며, 같은 날짜에 다시 저장하면 기존 내용이 덮어씌워져야 한다(Upsert).</t>
+        </is>
+      </c>
+      <c r="G102" s="91" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H102" s="91" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I102" s="91" t="inlineStr">
+        <is>
+          <t>PUT /diaries/{date} upsert, GET /diaries/{date} 조회</t>
+        </is>
+      </c>
+      <c r="J102" s="91" t="inlineStr">
         <is>
           <t>개발완료</t>
         </is>
       </c>
-      <c r="K102" s="42" t="n"/>
+      <c r="K102" s="91" t="n"/>
     </row>
     <row r="103" ht="22.5" customHeight="1" s="92">
-      <c r="A103" s="14" t="inlineStr">
-        <is>
-          <t>REQ-130</t>
-        </is>
-      </c>
-      <c r="B103" s="32" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="C103" s="32" t="inlineStr">
-        <is>
-          <t>JTI 블랙리스트 토큰 폐기</t>
-        </is>
-      </c>
-      <c r="D103" s="32" t="n"/>
-      <c r="E103" s="32" t="n"/>
-      <c r="F103" s="33" t="inlineStr">
-        <is>
-          <t>모든 JWT에 고유 JTI(JWT ID) 클레임을 포함하고, 로그아웃/탈퇴 시 JTI를 Redis 블랙리스트에 등록하여 즉시 무효화해야 한다. Redis 장애 시 안전 우선(fail-closed) 정책을 적용한다.</t>
-        </is>
-      </c>
-      <c r="G103" s="34" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H103" s="44" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I103" s="59" t="inlineStr">
-        <is>
-          <t>Redis TTL 기반, fail-closed</t>
-        </is>
-      </c>
-      <c r="J103" s="14" t="inlineStr">
+      <c r="A103" s="91" t="inlineStr">
+        <is>
+          <t>REQ-074</t>
+        </is>
+      </c>
+      <c r="B103" s="91" t="inlineStr">
+        <is>
+          <t>일기</t>
+        </is>
+      </c>
+      <c r="C103" s="91" t="inlineStr">
+        <is>
+          <t>일기 기간 목록 조회</t>
+        </is>
+      </c>
+      <c r="D103" s="91" t="n"/>
+      <c r="E103" s="91" t="n"/>
+      <c r="F103" s="91" t="inlineStr">
+        <is>
+          <t>일반 사용자는 시작일과 종료일을 지정하여 해당 기간의 일기 목록을 조회할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G103" s="91" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H103" s="91" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I103" s="91" t="inlineStr">
+        <is>
+          <t>GET /diaries?start={date}&amp;end={date}</t>
+        </is>
+      </c>
+      <c r="J103" s="91" t="inlineStr">
         <is>
           <t>개발완료</t>
         </is>
       </c>
-      <c r="K103" s="42" t="n"/>
+      <c r="K103" s="91" t="n"/>
     </row>
     <row r="104" ht="22.5" customHeight="1" s="92">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>REQ-131</t>
+          <t>REQ-129</t>
         </is>
       </c>
       <c r="B104" s="32" t="inlineStr">
@@ -5632,14 +5632,14 @@
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>CORS 정책</t>
+          <t>JWT 토큰 로테이션</t>
         </is>
       </c>
       <c r="D104" s="32" t="n"/>
       <c r="E104" s="32" t="n"/>
       <c r="F104" s="33" t="inlineStr">
         <is>
-          <t>운영환경에서 FRONTEND_ORIGIN 환경변수에 명시된 도메인만 cross-origin 요청을 허용하고, 미설정 시 모든 cross-origin 요청을 차단해야 한다.</t>
+          <t>토큰 재발급 시 기존 refresh token을 즉시 폐기하고 새 refresh token을 발급(로테이션)하여, 탈취된 토큰의 재사용을 방지해야 한다.</t>
         </is>
       </c>
       <c r="G104" s="34" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="I104" s="59" t="inlineStr">
         <is>
-          <t>credentials 포함</t>
+          <t>Refresh Token Rotation</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <row r="105" ht="22.5" customHeight="1" s="92">
       <c r="A105" s="14" t="inlineStr">
         <is>
-          <t>REQ-132</t>
+          <t>REQ-130</t>
         </is>
       </c>
       <c r="B105" s="32" t="inlineStr">
@@ -5677,14 +5677,14 @@
       </c>
       <c r="C105" s="32" t="inlineStr">
         <is>
-          <t>비밀번호 강도 검증</t>
+          <t>JTI 블랙리스트 토큰 폐기</t>
         </is>
       </c>
       <c r="D105" s="32" t="n"/>
       <c r="E105" s="32" t="n"/>
       <c r="F105" s="33" t="inlineStr">
         <is>
-          <t>회원가입 시 비밀번호는 최소 8자, 대문자/소문자/숫자/특수문자 각 1자 이상을 포함해야 하며, 미충족 시 가입을 거부해야 한다.</t>
+          <t>모든 JWT에 고유 JTI(JWT ID) 클레임을 포함하고, 로그아웃/탈퇴 시 JTI를 Redis 블랙리스트에 등록하여 즉시 무효화해야 한다. Redis 장애 시 안전 우선(fail-closed) 정책을 적용한다.</t>
         </is>
       </c>
       <c r="G105" s="34" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="I105" s="59" t="inlineStr">
         <is>
-          <t>정규식 검증</t>
+          <t>Redis TTL 기반, fail-closed</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -5712,24 +5712,24 @@
     <row r="106" ht="22.5" customHeight="1" s="92">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>REQ-133</t>
+          <t>REQ-131</t>
         </is>
       </c>
       <c r="B106" s="32" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
         <is>
-          <t>Nginx 요청 속도 제한</t>
+          <t>CORS 정책</t>
         </is>
       </c>
       <c r="D106" s="32" t="n"/>
       <c r="E106" s="32" t="n"/>
       <c r="F106" s="33" t="inlineStr">
         <is>
-          <t>Nginx 리버스 프록시에서 인증 API(5req/s), OCR API(3req/s), 일반 API(30req/s) 별로 요청 속도를 제한하고, 초과 시 429를 반환해야 한다.</t>
+          <t>운영환경에서 FRONTEND_ORIGIN 환경변수에 명시된 도메인만 cross-origin 요청을 허용하고, 미설정 시 모든 cross-origin 요청을 차단해야 한다.</t>
         </is>
       </c>
       <c r="G106" s="34" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="I106" s="59" t="inlineStr">
         <is>
-          <t>burst 허용</t>
+          <t>credentials 포함</t>
         </is>
       </c>
       <c r="J106" s="14" t="inlineStr">
@@ -5757,24 +5757,24 @@
     <row r="107" ht="22.5" customHeight="1" s="92">
       <c r="A107" s="14" t="inlineStr">
         <is>
-          <t>REQ-134</t>
+          <t>REQ-132</t>
         </is>
       </c>
       <c r="B107" s="32" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
         <is>
-          <t>Docker 컨테이너화</t>
+          <t>비밀번호 강도 검증</t>
         </is>
       </c>
       <c r="D107" s="32" t="n"/>
       <c r="E107" s="32" t="n"/>
       <c r="F107" s="33" t="inlineStr">
         <is>
-          <t>API 서버, AI 워커, MySQL, Redis, ChromaDB, Nginx를 Docker Compose로 구성하고, 서비스 간 네트워크를 frontend/backend로 분리해야 한다.</t>
+          <t>회원가입 시 비밀번호는 최소 8자, 대문자/소문자/숫자/특수문자 각 1자 이상을 포함해야 하며, 미충족 시 가입을 거부해야 한다.</t>
         </is>
       </c>
       <c r="G107" s="34" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I107" s="59" t="inlineStr">
         <is>
-          <t>멀티 서비스 구성</t>
+          <t>정규식 검증</t>
         </is>
       </c>
       <c r="J107" s="14" t="inlineStr">
@@ -5802,24 +5802,24 @@
     <row r="108" ht="22.5" customHeight="1" s="92">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>REQ-135</t>
+          <t>REQ-133</t>
         </is>
       </c>
       <c r="B108" s="32" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>성능</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
         <is>
-          <t>프론트엔드 토큰 자동 갱신</t>
+          <t>Nginx 요청 속도 제한</t>
         </is>
       </c>
       <c r="D108" s="32" t="n"/>
       <c r="E108" s="32" t="n"/>
       <c r="F108" s="33" t="inlineStr">
         <is>
-          <t>프론트엔드는 API 호출 시 401 응답을 수신하면 자동으로 토큰 재발급을 시도하고, 원래 요청을 재실행해야 한다. 동시 다발 401 시 재발급 요청을 단일화(deduplication)한다.</t>
+          <t>Nginx 리버스 프록시에서 인증 API(5req/s), OCR API(3req/s), 일반 API(30req/s) 별로 요청 속도를 제한하고, 초과 시 429를 반환해야 한다.</t>
         </is>
       </c>
       <c r="G108" s="34" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="I108" s="59" t="inlineStr">
         <is>
-          <t>무중단 사용자 경험</t>
+          <t>burst 허용</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
@@ -5847,24 +5847,24 @@
     <row r="109" ht="22.5" customHeight="1" s="92">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>REQ-136</t>
+          <t>REQ-134</t>
         </is>
       </c>
       <c r="B109" s="32" t="inlineStr">
         <is>
-          <t>프라이버시</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
         <is>
-          <t>사용자 전환 데이터 격리</t>
+          <t>Docker 컨테이너화</t>
         </is>
       </c>
       <c r="D109" s="32" t="n"/>
       <c r="E109" s="32" t="n"/>
       <c r="F109" s="33" t="inlineStr">
         <is>
-          <t>동일 기기에서 다른 사용자로 로그인 시 이전 사용자의 OCR/가이드/챗봇 세션 등 로컬 데이터를 자동 정리하여 데이터 유출을 방지해야 한다.</t>
+          <t>API 서버, AI 워커, MySQL, Redis, ChromaDB, Nginx를 Docker Compose로 구성하고, 서비스 간 네트워크를 frontend/backend로 분리해야 한다.</t>
         </is>
       </c>
       <c r="G109" s="34" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="I109" s="59" t="inlineStr">
         <is>
-          <t>localStorage 클린업</t>
+          <t>멀티 서비스 구성</t>
         </is>
       </c>
       <c r="J109" s="14" t="inlineStr">
@@ -5892,24 +5892,24 @@
     <row r="110" ht="22.5" customHeight="1" s="92">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>REQ-137</t>
+          <t>REQ-135</t>
         </is>
       </c>
       <c r="B110" s="32" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
         <is>
-          <t>DB 마이그레이션 자동 적용</t>
+          <t>프론트엔드 토큰 자동 갱신</t>
         </is>
       </c>
       <c r="D110" s="32" t="n"/>
       <c r="E110" s="32" t="n"/>
       <c r="F110" s="33" t="inlineStr">
         <is>
-          <t>서버 기동 시 pending 상태의 데이터베이스 마이그레이션을 자동으로 감지하고 순차 적용해야 한다.</t>
+          <t>프론트엔드는 API 호출 시 401 응답을 수신하면 자동으로 토큰 재발급을 시도하고, 원래 요청을 재실행해야 한다. 동시 다발 401 시 재발급 요청을 단일화(deduplication)한다.</t>
         </is>
       </c>
       <c r="G110" s="34" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="H110" s="44" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I110" s="59" t="inlineStr">
         <is>
-          <t>Aerich 호환</t>
+          <t>무중단 사용자 경험</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
@@ -5937,162 +5937,226 @@
     <row r="111" ht="22.5" customHeight="1" s="92">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>REQ-138</t>
+          <t>REQ-136</t>
         </is>
       </c>
       <c r="B111" s="32" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>프라이버시</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
         <is>
-          <t>Nginx 보안 헤더</t>
+          <t>사용자 전환 데이터 격리</t>
         </is>
       </c>
       <c r="D111" s="32" t="n"/>
       <c r="E111" s="32" t="n"/>
       <c r="F111" s="33" t="inlineStr">
         <is>
+          <t>동일 기기에서 다른 사용자로 로그인 시 이전 사용자의 OCR/가이드/챗봇 세션 등 로컬 데이터를 자동 정리하여 데이터 유출을 방지해야 한다.</t>
+        </is>
+      </c>
+      <c r="G111" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H111" s="44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I111" s="59" t="inlineStr">
+        <is>
+          <t>localStorage 클린업</t>
+        </is>
+      </c>
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K111" s="42" t="n"/>
+    </row>
+    <row r="112" ht="22.5" customHeight="1" s="92">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>REQ-137</t>
+        </is>
+      </c>
+      <c r="B112" s="32" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>DB 마이그레이션 자동 적용</t>
+        </is>
+      </c>
+      <c r="D112" s="32" t="n"/>
+      <c r="E112" s="32" t="n"/>
+      <c r="F112" s="33" t="inlineStr">
+        <is>
+          <t>서버 기동 시 pending 상태의 데이터베이스 마이그레이션을 자동으로 감지하고 순차 적용해야 한다.</t>
+        </is>
+      </c>
+      <c r="G112" s="34" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H112" s="44" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I112" s="59" t="inlineStr">
+        <is>
+          <t>Aerich 호환</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
+      <c r="K112" s="42" t="n"/>
+    </row>
+    <row r="113" ht="22.5" customHeight="1" s="92">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>REQ-138</t>
+        </is>
+      </c>
+      <c r="B113" s="32" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>Nginx 보안 헤더</t>
+        </is>
+      </c>
+      <c r="D113" s="32" t="n"/>
+      <c r="E113" s="32" t="n"/>
+      <c r="F113" s="33" t="inlineStr">
+        <is>
           <t>Nginx에서 X-Content-Type-Options(nosniff), X-Frame-Options(DENY), X-XSS-Protection(1; mode=block) 보안 헤더를 모든 응답에 포함해야 한다.</t>
         </is>
       </c>
-      <c r="G111" s="34" t="inlineStr">
+      <c r="G113" s="34" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H111" s="44" t="inlineStr">
+      <c r="H113" s="44" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I111" s="59" t="inlineStr">
+      <c r="I113" s="59" t="inlineStr">
         <is>
           <t>OWASP 권장</t>
         </is>
       </c>
-      <c r="J111" s="14" t="inlineStr">
+      <c r="J113" s="14" t="inlineStr">
         <is>
           <t>개발완료</t>
         </is>
       </c>
-      <c r="K111" s="42" t="n"/>
-    </row>
-    <row r="112" ht="22.5" customHeight="1" s="92">
-      <c r="A112" s="60" t="inlineStr">
+      <c r="K113" s="42" t="n"/>
+    </row>
+    <row r="114" ht="22.5" customHeight="1" s="92">
+      <c r="A114" s="60" t="inlineStr">
         <is>
           <t>REQ-075</t>
         </is>
       </c>
-      <c r="B112" s="61" t="inlineStr">
+      <c r="B114" s="61" t="inlineStr">
         <is>
           <t>가이드</t>
         </is>
       </c>
-      <c r="C112" s="61" t="inlineStr">
+      <c r="C114" s="61" t="inlineStr">
         <is>
           <t>가이드 피드백 수집</t>
         </is>
       </c>
-      <c r="D112" s="61" t="n"/>
-      <c r="E112" s="72" t="n"/>
-      <c r="F112" s="62" t="inlineStr">
-        <is>
-          <t>일반 사용자는 생성된 가이드에 대해 별점(1~5), 도움 여부, 코멘트를 제출할 수 있어야 하며, 가이드당 사용자 1회만 허용한다. 피드백에는 가이드 생성 시 사용된 프롬프트 버전이 자동 기록된다.</t>
-        </is>
-      </c>
-      <c r="G112" s="63" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H112" s="76" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I112" s="62" t="inlineStr">
-        <is>
-          <t>unique(guide_job_id, user_id), rating 1~5 검증, comment 최대 1000자</t>
-        </is>
-      </c>
-      <c r="J112" s="72" t="inlineStr">
-        <is>
-          <t>개발완료</t>
-        </is>
-      </c>
-      <c r="K112" s="37" t="n"/>
-    </row>
-    <row r="113" ht="22.5" customHeight="1" s="92">
-      <c r="A113" s="66" t="inlineStr">
-        <is>
-          <t>REQ-076</t>
-        </is>
-      </c>
-      <c r="B113" s="67" t="inlineStr">
-        <is>
-          <t>가이드</t>
-        </is>
-      </c>
-      <c r="C113" s="67" t="inlineStr">
-        <is>
-          <t>가이드 피드백 통계 조회</t>
-        </is>
-      </c>
-      <c r="D113" s="67" t="n"/>
-      <c r="E113" s="74" t="n"/>
-      <c r="F113" s="68" t="inlineStr">
-        <is>
-          <t>시스템은 프롬프트 버전별 평균 평점, 도움됨 비율을 집계하여 반환할 수 있어야 하며, 이를 통해 저평점 프롬프트 버전 식별 및 개선 판단 근거를 제공한다.</t>
-        </is>
-      </c>
-      <c r="G113" s="69" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H113" s="75" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I113" s="68" t="inlineStr">
-        <is>
-          <t>prompt_version별 그룹 집계</t>
-        </is>
-      </c>
-      <c r="J113" s="74" t="inlineStr">
-        <is>
-          <t>개발완료</t>
-        </is>
-      </c>
-      <c r="K113" s="42" t="n"/>
-    </row>
-    <row r="114" ht="22.5" customHeight="1" s="92">
-      <c r="A114" s="60" t="n"/>
-      <c r="B114" s="61" t="n"/>
-      <c r="C114" s="61" t="n"/>
       <c r="D114" s="61" t="n"/>
       <c r="E114" s="72" t="n"/>
-      <c r="F114" s="62" t="n"/>
-      <c r="G114" s="63" t="n"/>
-      <c r="H114" s="73" t="n"/>
-      <c r="I114" s="62" t="n"/>
-      <c r="J114" s="72" t="n"/>
+      <c r="F114" s="62" t="inlineStr">
+        <is>
+          <t>일반 사용자는 생성된 가이드에 대해 별점(1~5), 도움 여부, 코멘트를 제출할 수 있어야 하며, 가이드당 사용자 1회만 허용한다. 피드백에는 가이드 생성 시 사용된 프롬프트 버전이 자동 기록된다.</t>
+        </is>
+      </c>
+      <c r="G114" s="63" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H114" s="76" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I114" s="62" t="inlineStr">
+        <is>
+          <t>unique(guide_job_id, user_id), rating 1~5 검증, comment 최대 1000자</t>
+        </is>
+      </c>
+      <c r="J114" s="72" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K114" s="37" t="n"/>
     </row>
     <row r="115" ht="22.5" customHeight="1" s="92">
-      <c r="A115" s="66" t="n"/>
-      <c r="B115" s="67" t="n"/>
-      <c r="C115" s="67" t="n"/>
-      <c r="D115" s="74" t="n"/>
+      <c r="A115" s="66" t="inlineStr">
+        <is>
+          <t>REQ-076</t>
+        </is>
+      </c>
+      <c r="B115" s="67" t="inlineStr">
+        <is>
+          <t>가이드</t>
+        </is>
+      </c>
+      <c r="C115" s="67" t="inlineStr">
+        <is>
+          <t>가이드 피드백 통계 조회</t>
+        </is>
+      </c>
+      <c r="D115" s="67" t="n"/>
       <c r="E115" s="74" t="n"/>
-      <c r="F115" s="68" t="n"/>
-      <c r="G115" s="69" t="n"/>
-      <c r="H115" s="75" t="n"/>
-      <c r="I115" s="68" t="n"/>
-      <c r="J115" s="74" t="n"/>
+      <c r="F115" s="68" t="inlineStr">
+        <is>
+          <t>시스템은 프롬프트 버전별 평균 평점, 도움됨 비율을 집계하여 반환할 수 있어야 하며, 이를 통해 저평점 프롬프트 버전 식별 및 개선 판단 근거를 제공한다.</t>
+        </is>
+      </c>
+      <c r="G115" s="69" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H115" s="75" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I115" s="68" t="inlineStr">
+        <is>
+          <t>prompt_version별 그룹 집계</t>
+        </is>
+      </c>
+      <c r="J115" s="74" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="K115" s="42" t="n"/>
     </row>
     <row r="116" ht="22.5" customHeight="1" s="92">
@@ -6103,7 +6167,7 @@
       <c r="E116" s="72" t="n"/>
       <c r="F116" s="62" t="n"/>
       <c r="G116" s="63" t="n"/>
-      <c r="H116" s="76" t="n"/>
+      <c r="H116" s="73" t="n"/>
       <c r="I116" s="62" t="n"/>
       <c r="J116" s="72" t="n"/>
       <c r="K116" s="37" t="n"/>
@@ -6117,7 +6181,7 @@
       <c r="F117" s="68" t="n"/>
       <c r="G117" s="69" t="n"/>
       <c r="H117" s="75" t="n"/>
-      <c r="I117" s="74" t="n"/>
+      <c r="I117" s="68" t="n"/>
       <c r="J117" s="74" t="n"/>
       <c r="K117" s="42" t="n"/>
     </row>
@@ -6125,11 +6189,11 @@
       <c r="A118" s="60" t="n"/>
       <c r="B118" s="61" t="n"/>
       <c r="C118" s="61" t="n"/>
-      <c r="D118" s="72" t="n"/>
+      <c r="D118" s="61" t="n"/>
       <c r="E118" s="72" t="n"/>
       <c r="F118" s="62" t="n"/>
       <c r="G118" s="63" t="n"/>
-      <c r="H118" s="73" t="n"/>
+      <c r="H118" s="76" t="n"/>
       <c r="I118" s="62" t="n"/>
       <c r="J118" s="72" t="n"/>
       <c r="K118" s="37" t="n"/>
@@ -6143,7 +6207,7 @@
       <c r="F119" s="68" t="n"/>
       <c r="G119" s="69" t="n"/>
       <c r="H119" s="75" t="n"/>
-      <c r="I119" s="68" t="n"/>
+      <c r="I119" s="74" t="n"/>
       <c r="J119" s="74" t="n"/>
       <c r="K119" s="42" t="n"/>
     </row>
@@ -6177,12 +6241,12 @@
       <c r="A122" s="60" t="n"/>
       <c r="B122" s="61" t="n"/>
       <c r="C122" s="61" t="n"/>
-      <c r="D122" s="61" t="n"/>
+      <c r="D122" s="72" t="n"/>
       <c r="E122" s="72" t="n"/>
       <c r="F122" s="62" t="n"/>
       <c r="G122" s="63" t="n"/>
-      <c r="H122" s="78" t="n"/>
-      <c r="I122" s="79" t="n"/>
+      <c r="H122" s="73" t="n"/>
+      <c r="I122" s="62" t="n"/>
       <c r="J122" s="72" t="n"/>
       <c r="K122" s="37" t="n"/>
     </row>
@@ -6203,12 +6267,12 @@
       <c r="A124" s="60" t="n"/>
       <c r="B124" s="61" t="n"/>
       <c r="C124" s="61" t="n"/>
-      <c r="D124" s="72" t="n"/>
+      <c r="D124" s="61" t="n"/>
       <c r="E124" s="72" t="n"/>
       <c r="F124" s="62" t="n"/>
       <c r="G124" s="63" t="n"/>
-      <c r="H124" s="76" t="n"/>
-      <c r="I124" s="62" t="n"/>
+      <c r="H124" s="78" t="n"/>
+      <c r="I124" s="79" t="n"/>
       <c r="J124" s="72" t="n"/>
       <c r="K124" s="37" t="n"/>
     </row>
@@ -6220,7 +6284,7 @@
       <c r="E125" s="74" t="n"/>
       <c r="F125" s="68" t="n"/>
       <c r="G125" s="69" t="n"/>
-      <c r="H125" s="77" t="n"/>
+      <c r="H125" s="75" t="n"/>
       <c r="I125" s="68" t="n"/>
       <c r="J125" s="74" t="n"/>
       <c r="K125" s="42" t="n"/>
@@ -6229,11 +6293,11 @@
       <c r="A126" s="60" t="n"/>
       <c r="B126" s="61" t="n"/>
       <c r="C126" s="61" t="n"/>
-      <c r="D126" s="61" t="n"/>
+      <c r="D126" s="72" t="n"/>
       <c r="E126" s="72" t="n"/>
       <c r="F126" s="62" t="n"/>
       <c r="G126" s="63" t="n"/>
-      <c r="H126" s="73" t="n"/>
+      <c r="H126" s="76" t="n"/>
       <c r="I126" s="62" t="n"/>
       <c r="J126" s="72" t="n"/>
       <c r="K126" s="37" t="n"/>
@@ -6242,11 +6306,11 @@
       <c r="A127" s="66" t="n"/>
       <c r="B127" s="67" t="n"/>
       <c r="C127" s="67" t="n"/>
-      <c r="D127" s="67" t="n"/>
-      <c r="E127" s="67" t="n"/>
+      <c r="D127" s="74" t="n"/>
+      <c r="E127" s="74" t="n"/>
       <c r="F127" s="68" t="n"/>
       <c r="G127" s="69" t="n"/>
-      <c r="H127" s="75" t="n"/>
+      <c r="H127" s="77" t="n"/>
       <c r="I127" s="68" t="n"/>
       <c r="J127" s="74" t="n"/>
       <c r="K127" s="42" t="n"/>
@@ -6259,7 +6323,7 @@
       <c r="E128" s="72" t="n"/>
       <c r="F128" s="62" t="n"/>
       <c r="G128" s="63" t="n"/>
-      <c r="H128" s="76" t="n"/>
+      <c r="H128" s="73" t="n"/>
       <c r="I128" s="62" t="n"/>
       <c r="J128" s="72" t="n"/>
       <c r="K128" s="37" t="n"/>
@@ -6269,10 +6333,10 @@
       <c r="B129" s="67" t="n"/>
       <c r="C129" s="67" t="n"/>
       <c r="D129" s="67" t="n"/>
-      <c r="E129" s="74" t="n"/>
+      <c r="E129" s="67" t="n"/>
       <c r="F129" s="68" t="n"/>
       <c r="G129" s="69" t="n"/>
-      <c r="H129" s="77" t="n"/>
+      <c r="H129" s="75" t="n"/>
       <c r="I129" s="68" t="n"/>
       <c r="J129" s="74" t="n"/>
       <c r="K129" s="42" t="n"/>
@@ -6281,11 +6345,11 @@
       <c r="A130" s="60" t="n"/>
       <c r="B130" s="61" t="n"/>
       <c r="C130" s="61" t="n"/>
-      <c r="D130" s="72" t="n"/>
+      <c r="D130" s="61" t="n"/>
       <c r="E130" s="72" t="n"/>
       <c r="F130" s="62" t="n"/>
       <c r="G130" s="63" t="n"/>
-      <c r="H130" s="73" t="n"/>
+      <c r="H130" s="76" t="n"/>
       <c r="I130" s="62" t="n"/>
       <c r="J130" s="72" t="n"/>
       <c r="K130" s="37" t="n"/>
@@ -6294,11 +6358,11 @@
       <c r="A131" s="66" t="n"/>
       <c r="B131" s="67" t="n"/>
       <c r="C131" s="67" t="n"/>
-      <c r="D131" s="74" t="n"/>
+      <c r="D131" s="67" t="n"/>
       <c r="E131" s="74" t="n"/>
       <c r="F131" s="68" t="n"/>
       <c r="G131" s="69" t="n"/>
-      <c r="H131" s="75" t="n"/>
+      <c r="H131" s="77" t="n"/>
       <c r="I131" s="68" t="n"/>
       <c r="J131" s="74" t="n"/>
       <c r="K131" s="42" t="n"/>
@@ -6307,7 +6371,7 @@
       <c r="A132" s="60" t="n"/>
       <c r="B132" s="61" t="n"/>
       <c r="C132" s="61" t="n"/>
-      <c r="D132" s="61" t="n"/>
+      <c r="D132" s="72" t="n"/>
       <c r="E132" s="72" t="n"/>
       <c r="F132" s="62" t="n"/>
       <c r="G132" s="63" t="n"/>
@@ -6320,8 +6384,8 @@
       <c r="A133" s="66" t="n"/>
       <c r="B133" s="67" t="n"/>
       <c r="C133" s="67" t="n"/>
-      <c r="D133" s="67" t="n"/>
-      <c r="E133" s="67" t="n"/>
+      <c r="D133" s="74" t="n"/>
+      <c r="E133" s="74" t="n"/>
       <c r="F133" s="68" t="n"/>
       <c r="G133" s="69" t="n"/>
       <c r="H133" s="75" t="n"/>
@@ -6334,7 +6398,7 @@
       <c r="B134" s="61" t="n"/>
       <c r="C134" s="61" t="n"/>
       <c r="D134" s="61" t="n"/>
-      <c r="E134" s="61" t="n"/>
+      <c r="E134" s="72" t="n"/>
       <c r="F134" s="62" t="n"/>
       <c r="G134" s="63" t="n"/>
       <c r="H134" s="73" t="n"/>
@@ -6346,11 +6410,11 @@
       <c r="A135" s="66" t="n"/>
       <c r="B135" s="67" t="n"/>
       <c r="C135" s="67" t="n"/>
-      <c r="D135" s="74" t="n"/>
-      <c r="E135" s="74" t="n"/>
+      <c r="D135" s="67" t="n"/>
+      <c r="E135" s="67" t="n"/>
       <c r="F135" s="68" t="n"/>
       <c r="G135" s="69" t="n"/>
-      <c r="H135" s="77" t="n"/>
+      <c r="H135" s="75" t="n"/>
       <c r="I135" s="68" t="n"/>
       <c r="J135" s="74" t="n"/>
       <c r="K135" s="42" t="n"/>
@@ -6360,10 +6424,10 @@
       <c r="B136" s="61" t="n"/>
       <c r="C136" s="61" t="n"/>
       <c r="D136" s="61" t="n"/>
-      <c r="E136" s="72" t="n"/>
+      <c r="E136" s="61" t="n"/>
       <c r="F136" s="62" t="n"/>
       <c r="G136" s="63" t="n"/>
-      <c r="H136" s="76" t="n"/>
+      <c r="H136" s="73" t="n"/>
       <c r="I136" s="62" t="n"/>
       <c r="J136" s="72" t="n"/>
       <c r="K136" s="37" t="n"/>
@@ -6372,12 +6436,12 @@
       <c r="A137" s="66" t="n"/>
       <c r="B137" s="67" t="n"/>
       <c r="C137" s="67" t="n"/>
-      <c r="D137" s="67" t="n"/>
-      <c r="E137" s="67" t="n"/>
+      <c r="D137" s="74" t="n"/>
+      <c r="E137" s="74" t="n"/>
       <c r="F137" s="68" t="n"/>
       <c r="G137" s="69" t="n"/>
-      <c r="H137" s="70" t="n"/>
-      <c r="I137" s="80" t="n"/>
+      <c r="H137" s="77" t="n"/>
+      <c r="I137" s="68" t="n"/>
       <c r="J137" s="74" t="n"/>
       <c r="K137" s="42" t="n"/>
     </row>
@@ -6388,8 +6452,8 @@
       <c r="D138" s="61" t="n"/>
       <c r="E138" s="72" t="n"/>
       <c r="F138" s="62" t="n"/>
-      <c r="G138" s="72" t="n"/>
-      <c r="H138" s="72" t="n"/>
+      <c r="G138" s="63" t="n"/>
+      <c r="H138" s="76" t="n"/>
       <c r="I138" s="62" t="n"/>
       <c r="J138" s="72" t="n"/>
       <c r="K138" s="37" t="n"/>
@@ -6399,11 +6463,11 @@
       <c r="B139" s="67" t="n"/>
       <c r="C139" s="67" t="n"/>
       <c r="D139" s="67" t="n"/>
-      <c r="E139" s="74" t="n"/>
+      <c r="E139" s="67" t="n"/>
       <c r="F139" s="68" t="n"/>
-      <c r="G139" s="74" t="n"/>
-      <c r="H139" s="74" t="n"/>
-      <c r="I139" s="68" t="n"/>
+      <c r="G139" s="69" t="n"/>
+      <c r="H139" s="70" t="n"/>
+      <c r="I139" s="80" t="n"/>
       <c r="J139" s="74" t="n"/>
       <c r="K139" s="42" t="n"/>
     </row>
@@ -6411,11 +6475,11 @@
       <c r="A140" s="60" t="n"/>
       <c r="B140" s="61" t="n"/>
       <c r="C140" s="61" t="n"/>
-      <c r="D140" s="72" t="n"/>
+      <c r="D140" s="61" t="n"/>
       <c r="E140" s="72" t="n"/>
       <c r="F140" s="62" t="n"/>
-      <c r="G140" s="63" t="n"/>
-      <c r="H140" s="73" t="n"/>
+      <c r="G140" s="72" t="n"/>
+      <c r="H140" s="72" t="n"/>
       <c r="I140" s="62" t="n"/>
       <c r="J140" s="72" t="n"/>
       <c r="K140" s="37" t="n"/>
@@ -6424,11 +6488,11 @@
       <c r="A141" s="66" t="n"/>
       <c r="B141" s="67" t="n"/>
       <c r="C141" s="67" t="n"/>
-      <c r="D141" s="74" t="n"/>
+      <c r="D141" s="67" t="n"/>
       <c r="E141" s="74" t="n"/>
       <c r="F141" s="68" t="n"/>
-      <c r="G141" s="69" t="n"/>
-      <c r="H141" s="75" t="n"/>
+      <c r="G141" s="74" t="n"/>
+      <c r="H141" s="74" t="n"/>
       <c r="I141" s="68" t="n"/>
       <c r="J141" s="74" t="n"/>
       <c r="K141" s="42" t="n"/>
@@ -6493,7 +6557,7 @@
       <c r="E146" s="72" t="n"/>
       <c r="F146" s="62" t="n"/>
       <c r="G146" s="63" t="n"/>
-      <c r="H146" s="76" t="n"/>
+      <c r="H146" s="73" t="n"/>
       <c r="I146" s="62" t="n"/>
       <c r="J146" s="72" t="n"/>
       <c r="K146" s="37" t="n"/>
@@ -6502,7 +6566,7 @@
       <c r="A147" s="66" t="n"/>
       <c r="B147" s="67" t="n"/>
       <c r="C147" s="67" t="n"/>
-      <c r="D147" s="67" t="n"/>
+      <c r="D147" s="74" t="n"/>
       <c r="E147" s="74" t="n"/>
       <c r="F147" s="68" t="n"/>
       <c r="G147" s="69" t="n"/>
@@ -6515,7 +6579,7 @@
       <c r="A148" s="60" t="n"/>
       <c r="B148" s="61" t="n"/>
       <c r="C148" s="61" t="n"/>
-      <c r="D148" s="61" t="n"/>
+      <c r="D148" s="72" t="n"/>
       <c r="E148" s="72" t="n"/>
       <c r="F148" s="62" t="n"/>
       <c r="G148" s="63" t="n"/>
@@ -6528,7 +6592,7 @@
       <c r="A149" s="66" t="n"/>
       <c r="B149" s="67" t="n"/>
       <c r="C149" s="67" t="n"/>
-      <c r="D149" s="74" t="n"/>
+      <c r="D149" s="67" t="n"/>
       <c r="E149" s="74" t="n"/>
       <c r="F149" s="68" t="n"/>
       <c r="G149" s="69" t="n"/>
@@ -6545,7 +6609,7 @@
       <c r="E150" s="72" t="n"/>
       <c r="F150" s="62" t="n"/>
       <c r="G150" s="63" t="n"/>
-      <c r="H150" s="73" t="n"/>
+      <c r="H150" s="76" t="n"/>
       <c r="I150" s="62" t="n"/>
       <c r="J150" s="72" t="n"/>
       <c r="K150" s="37" t="n"/>
@@ -6567,7 +6631,7 @@
       <c r="A152" s="60" t="n"/>
       <c r="B152" s="61" t="n"/>
       <c r="C152" s="61" t="n"/>
-      <c r="D152" s="72" t="n"/>
+      <c r="D152" s="61" t="n"/>
       <c r="E152" s="72" t="n"/>
       <c r="F152" s="62" t="n"/>
       <c r="G152" s="63" t="n"/>
@@ -6610,7 +6674,7 @@
       <c r="E155" s="74" t="n"/>
       <c r="F155" s="68" t="n"/>
       <c r="G155" s="69" t="n"/>
-      <c r="H155" s="77" t="n"/>
+      <c r="H155" s="75" t="n"/>
       <c r="I155" s="68" t="n"/>
       <c r="J155" s="74" t="n"/>
       <c r="K155" s="42" t="n"/>
@@ -6623,7 +6687,7 @@
       <c r="E156" s="72" t="n"/>
       <c r="F156" s="62" t="n"/>
       <c r="G156" s="63" t="n"/>
-      <c r="H156" s="76" t="n"/>
+      <c r="H156" s="73" t="n"/>
       <c r="I156" s="62" t="n"/>
       <c r="J156" s="72" t="n"/>
       <c r="K156" s="37" t="n"/>
@@ -6723,11 +6787,11 @@
       <c r="A164" s="60" t="n"/>
       <c r="B164" s="61" t="n"/>
       <c r="C164" s="61" t="n"/>
-      <c r="D164" s="61" t="n"/>
+      <c r="D164" s="72" t="n"/>
       <c r="E164" s="72" t="n"/>
       <c r="F164" s="62" t="n"/>
       <c r="G164" s="63" t="n"/>
-      <c r="H164" s="73" t="n"/>
+      <c r="H164" s="76" t="n"/>
       <c r="I164" s="62" t="n"/>
       <c r="J164" s="72" t="n"/>
       <c r="K164" s="37" t="n"/>
@@ -6736,11 +6800,11 @@
       <c r="A165" s="66" t="n"/>
       <c r="B165" s="67" t="n"/>
       <c r="C165" s="67" t="n"/>
-      <c r="D165" s="67" t="n"/>
-      <c r="E165" s="67" t="n"/>
+      <c r="D165" s="74" t="n"/>
+      <c r="E165" s="74" t="n"/>
       <c r="F165" s="68" t="n"/>
       <c r="G165" s="69" t="n"/>
-      <c r="H165" s="75" t="n"/>
+      <c r="H165" s="77" t="n"/>
       <c r="I165" s="68" t="n"/>
       <c r="J165" s="74" t="n"/>
       <c r="K165" s="42" t="n"/>
@@ -6763,7 +6827,7 @@
       <c r="B167" s="67" t="n"/>
       <c r="C167" s="67" t="n"/>
       <c r="D167" s="67" t="n"/>
-      <c r="E167" s="74" t="n"/>
+      <c r="E167" s="67" t="n"/>
       <c r="F167" s="68" t="n"/>
       <c r="G167" s="69" t="n"/>
       <c r="H167" s="75" t="n"/>
@@ -6779,49 +6843,49 @@
       <c r="E168" s="72" t="n"/>
       <c r="F168" s="62" t="n"/>
       <c r="G168" s="63" t="n"/>
-      <c r="H168" s="76" t="n"/>
+      <c r="H168" s="73" t="n"/>
       <c r="I168" s="62" t="n"/>
       <c r="J168" s="72" t="n"/>
       <c r="K168" s="37" t="n"/>
     </row>
     <row r="169" ht="22.5" customHeight="1" s="92">
-      <c r="A169" s="81" t="n"/>
-      <c r="B169" s="82" t="n"/>
-      <c r="C169" s="82" t="n"/>
-      <c r="D169" s="82" t="n"/>
-      <c r="E169" s="83" t="n"/>
-      <c r="F169" s="84" t="n"/>
-      <c r="G169" s="85" t="n"/>
-      <c r="H169" s="86" t="n"/>
-      <c r="I169" s="84" t="n"/>
-      <c r="J169" s="83" t="n"/>
-      <c r="K169" s="87" t="n"/>
+      <c r="A169" s="66" t="n"/>
+      <c r="B169" s="67" t="n"/>
+      <c r="C169" s="67" t="n"/>
+      <c r="D169" s="67" t="n"/>
+      <c r="E169" s="74" t="n"/>
+      <c r="F169" s="68" t="n"/>
+      <c r="G169" s="69" t="n"/>
+      <c r="H169" s="75" t="n"/>
+      <c r="I169" s="68" t="n"/>
+      <c r="J169" s="74" t="n"/>
+      <c r="K169" s="42" t="n"/>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="92">
-      <c r="A170" s="91" t="n"/>
-      <c r="B170" s="91" t="n"/>
-      <c r="C170" s="91" t="n"/>
-      <c r="D170" s="91" t="n"/>
-      <c r="E170" s="91" t="n"/>
-      <c r="F170" s="91" t="n"/>
-      <c r="G170" s="91" t="n"/>
-      <c r="H170" s="91" t="n"/>
-      <c r="I170" s="91" t="n"/>
-      <c r="J170" s="91" t="n"/>
-      <c r="K170" s="91" t="n"/>
+      <c r="A170" s="60" t="n"/>
+      <c r="B170" s="61" t="n"/>
+      <c r="C170" s="61" t="n"/>
+      <c r="D170" s="61" t="n"/>
+      <c r="E170" s="72" t="n"/>
+      <c r="F170" s="62" t="n"/>
+      <c r="G170" s="63" t="n"/>
+      <c r="H170" s="76" t="n"/>
+      <c r="I170" s="62" t="n"/>
+      <c r="J170" s="72" t="n"/>
+      <c r="K170" s="37" t="n"/>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="92">
-      <c r="A171" s="91" t="n"/>
-      <c r="B171" s="91" t="n"/>
-      <c r="C171" s="91" t="n"/>
-      <c r="D171" s="91" t="n"/>
-      <c r="E171" s="91" t="n"/>
-      <c r="F171" s="91" t="n"/>
-      <c r="G171" s="91" t="n"/>
-      <c r="H171" s="91" t="n"/>
-      <c r="I171" s="91" t="n"/>
-      <c r="J171" s="91" t="n"/>
-      <c r="K171" s="91" t="n"/>
+      <c r="A171" s="81" t="n"/>
+      <c r="B171" s="82" t="n"/>
+      <c r="C171" s="82" t="n"/>
+      <c r="D171" s="82" t="n"/>
+      <c r="E171" s="83" t="n"/>
+      <c r="F171" s="84" t="n"/>
+      <c r="G171" s="85" t="n"/>
+      <c r="H171" s="86" t="n"/>
+      <c r="I171" s="84" t="n"/>
+      <c r="J171" s="83" t="n"/>
+      <c r="K171" s="87" t="n"/>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="92">
       <c r="A172" s="91" t="n"/>
@@ -17651,6 +17715,32 @@
       <c r="I1004" s="91" t="n"/>
       <c r="J1004" s="91" t="n"/>
       <c r="K1004" s="91" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="91" t="n"/>
+      <c r="B1005" s="91" t="n"/>
+      <c r="C1005" s="91" t="n"/>
+      <c r="D1005" s="91" t="n"/>
+      <c r="E1005" s="91" t="n"/>
+      <c r="F1005" s="91" t="n"/>
+      <c r="G1005" s="91" t="n"/>
+      <c r="H1005" s="91" t="n"/>
+      <c r="I1005" s="91" t="n"/>
+      <c r="J1005" s="91" t="n"/>
+      <c r="K1005" s="91" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="91" t="n"/>
+      <c r="B1006" s="91" t="n"/>
+      <c r="C1006" s="91" t="n"/>
+      <c r="D1006" s="91" t="n"/>
+      <c r="E1006" s="91" t="n"/>
+      <c r="F1006" s="91" t="n"/>
+      <c r="G1006" s="91" t="n"/>
+      <c r="H1006" s="91" t="n"/>
+      <c r="I1006" s="91" t="n"/>
+      <c r="J1006" s="91" t="n"/>
+      <c r="K1006" s="91" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1004">
